--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-dentaloral-bodystructure-ecs.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-dentaloral-bodystructure-ecs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-06</t>
+    <t>2025-06-24</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-dentaloral-bodystructure-ecs.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-observation-dentaloral-bodystructure-ecs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1697" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="181">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>JP Core Observation DentalOral BodyStructure Extension</t>
+    <t>JP Core Observation DentalOral BodyStructure IncludedStructure Extension</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -132,7 +132,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:Observation</t>
+    <t>element:Observation.bodySite</t>
   </si>
   <si>
     <t>ID</t>
@@ -2711,7 +2711,7 @@
         <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>77</v>
@@ -3230,7 +3230,7 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>77</v>
@@ -3749,7 +3749,7 @@
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>77</v>
@@ -3948,11 +3948,11 @@
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>77</v>
+        <v>129</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>79</v>
@@ -3970,12 +3970,14 @@
         <v>92</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>31</v>
+        <v>130</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>131</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>132</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -4039,7 +4041,7 @@
         <v>83</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31">
@@ -4057,10 +4059,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>77</v>
@@ -4787,7 +4789,7 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>77</v>
